--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.08406</v>
+        <v>17.42876</v>
       </c>
       <c r="D2" t="n">
-        <v>16.97459</v>
+        <v>17.03708</v>
       </c>
       <c r="E2" t="n">
-        <v>17.63941</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.62177</v>
+        <v>17.37627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0516</v>
+        <v>0.05163</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88776</v>
+        <v>1.85779</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.23439</v>
+        <v>17.40341</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03634</v>
+        <v>16.98839</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66221</v>
+        <v>17.26968</v>
       </c>
       <c r="F3" t="n">
-        <v>42.87625</v>
+        <v>43.88695</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05148</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87332</v>
+        <v>1.88535</v>
       </c>
     </row>
     <row r="4">
@@ -509,23 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>16.8748</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>17.57448</v>
+        <v>16.91249</v>
       </c>
       <c r="E4" t="n">
-        <v>17.1754</v>
+        <v>16.93359</v>
       </c>
       <c r="F4" t="n">
-        <v>43.93561</v>
+        <v>43.81683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0523</v>
+        <v>0.05127</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87811</v>
+        <v>1.86857</v>
       </c>
     </row>
     <row r="5">
@@ -534,23 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>17.28603</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>17.51529</v>
+        <v>16.85246</v>
       </c>
       <c r="E5" t="n">
-        <v>17.03864</v>
+        <v>17.03006</v>
       </c>
       <c r="F5" t="n">
-        <v>43.32862</v>
+        <v>44.1492</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05163</v>
+        <v>0.05157</v>
       </c>
       <c r="H5" t="n">
-        <v>1.88648</v>
+        <v>1.83286</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +561,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.42405</v>
+        <v>17.11704</v>
       </c>
       <c r="D6" t="n">
-        <v>17.37131</v>
+        <v>16.92218</v>
       </c>
       <c r="E6" t="n">
-        <v>17.3541</v>
+        <v>17.0297</v>
       </c>
       <c r="F6" t="n">
-        <v>44.22471</v>
+        <v>43.621</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05274</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.86556</v>
+        <v>0.05187</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.28004</v>
+        <v>17.30056</v>
       </c>
       <c r="D7" t="n">
-        <v>17.18015</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.91391</v>
+        <v>17.007</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>43.3185</v>
+        <v>43.84297</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05083</v>
+        <v>0.05243</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83801</v>
+        <v>1.84729</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.50702</v>
+        <v>17.46463</v>
       </c>
       <c r="D8" t="n">
-        <v>16.87376</v>
+        <v>17.15393</v>
       </c>
       <c r="E8" t="n">
-        <v>17.37656</v>
+        <v>17.16006</v>
       </c>
       <c r="F8" t="n">
-        <v>43.70093</v>
+        <v>43.55864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05284</v>
+        <v>0.05252</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85085</v>
+        <v>1.84797</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.00015</v>
+        <v>17.23164</v>
       </c>
       <c r="D9" t="n">
-        <v>16.93798</v>
+        <v>17.12905</v>
       </c>
       <c r="E9" t="n">
-        <v>17.00589</v>
+        <v>17.22815</v>
       </c>
       <c r="F9" t="n">
-        <v>43.83407</v>
+        <v>44.31145</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05233</v>
+        <v>0.05079</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85902</v>
+        <v>1.90492</v>
       </c>
     </row>
     <row r="10">
@@ -660,386 +663,156 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.55016</v>
+        <v>17.63678</v>
       </c>
       <c r="D10" t="n">
-        <v>16.89864</v>
+        <v>17.32156</v>
       </c>
       <c r="E10" t="n">
-        <v>17.14359</v>
+        <v>17.63347</v>
       </c>
       <c r="F10" t="n">
-        <v>43.28041</v>
+        <v>42.4371</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05127</v>
+        <v>0.05142</v>
       </c>
       <c r="H10" t="n">
-        <v>1.87021</v>
+        <v>1.86664</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>17.1574</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.70916</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.21687</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.37376</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05189</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.85997</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.31155</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>16.85957</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.08693</v>
-      </c>
-      <c r="F12" t="n">
-        <v>43.51011</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05227</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.88426</v>
+        <v>1.15602</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.92928</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17.06111</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.16793</v>
-      </c>
-      <c r="F13" t="n">
-        <v>44.38298</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.82943</v>
+        <v>1.16343</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.23544</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>17.17674</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.20745</v>
-      </c>
-      <c r="F14" t="n">
-        <v>44.60769</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05158</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.89791</v>
+        <v>1.14158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.34925</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>17.37752</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.06608</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.87438</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05216</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.8237</v>
+        <v>1.13766</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.37775</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>17.1287</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.1122</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.81382</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05175</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.87948</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.33727</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>17.23896</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.0765</v>
-      </c>
-      <c r="F17" t="n">
-        <v>43.25403</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0528</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.89049</v>
+        <v>1.16376</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.35562</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>17.34531</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.4881</v>
-      </c>
-      <c r="F18" t="n">
-        <v>44.10718</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05088</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.90385</v>
+        <v>1.16423</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.16596</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>17.69856</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17.06528</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.38137</v>
-      </c>
-      <c r="F19" t="n">
-        <v>45.13097</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05292</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.84133</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.63112</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.16312</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.62004</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.158</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.62625</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.15522</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.61153</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.13063</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.62549</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.13361</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.6243</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.16377</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.63173</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.1289</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.63125</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.15393</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.62884</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.14246</v>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.14575</v>
       </c>
     </row>
   </sheetData>
